--- a/excel2.xlsx
+++ b/excel2.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15140" activeTab="3"/>
+    <workbookView windowWidth="28000" windowHeight="12740" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="blockAreas" sheetId="1" r:id="rId1"/>
     <sheet name="plans" sheetId="6" r:id="rId2"/>
     <sheet name="instructions" sheetId="7" r:id="rId3"/>
-    <sheet name="QC1" sheetId="9" r:id="rId4"/>
-    <sheet name="QC2" sheetId="10" r:id="rId5"/>
-    <sheet name="QC3" sheetId="11" r:id="rId6"/>
+    <sheet name="qc1" sheetId="9" r:id="rId4"/>
+    <sheet name="qc2" sheetId="10" r:id="rId5"/>
+    <sheet name="qc3" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -85,43 +85,43 @@
     <t>IF</t>
   </si>
   <si>
-    <t>1A04</t>
-  </si>
-  <si>
-    <t>1A16</t>
-  </si>
-  <si>
-    <t>1B06</t>
-  </si>
-  <si>
-    <t>1B18</t>
-  </si>
-  <si>
-    <t>1C08</t>
-  </si>
-  <si>
-    <t>1C20</t>
-  </si>
-  <si>
-    <t>1D10</t>
-  </si>
-  <si>
-    <t>1D26</t>
+    <t>1A02</t>
+  </si>
+  <si>
+    <t>1A30</t>
+  </si>
+  <si>
+    <t>1B02</t>
+  </si>
+  <si>
+    <t>1B30</t>
+  </si>
+  <si>
+    <t>1C02</t>
+  </si>
+  <si>
+    <t>1C30</t>
+  </si>
+  <si>
+    <t>1D02</t>
+  </si>
+  <si>
+    <t>1D30</t>
   </si>
   <si>
     <t>IZ</t>
   </si>
   <si>
-    <t>1B10</t>
-  </si>
-  <si>
-    <t>1D12</t>
+    <t>1B22</t>
+  </si>
+  <si>
+    <t>1D22</t>
   </si>
   <si>
     <t>QZ</t>
   </si>
   <si>
-    <t>1C12</t>
+    <t>1C18</t>
   </si>
   <si>
     <t>type</t>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1343,7 +1343,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1357,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1371,7 +1371,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1385,7 +1385,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
